--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Real Madrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2138.680000000001</v>
+        <v>2465.760000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2134.82</v>
+        <v>2460.64</v>
       </c>
       <c r="D2" t="n">
-        <v>121.7432851481624</v>
+        <v>121.513102282333</v>
       </c>
       <c r="E2" t="n">
-        <v>108.8147946899504</v>
+        <v>110.7029065608947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5685279187817259</v>
+        <v>0.5683260126891166</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1434026582755626</v>
+        <v>0.1412429378531073</v>
       </c>
       <c r="H2" t="n">
-        <v>0.326133909287257</v>
+        <v>0.3188539741219963</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3288212069937958</v>
+        <v>0.3225963884821864</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="M2" t="n">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="N2" t="n">
-        <v>1022</v>
+        <v>1171</v>
       </c>
       <c r="O2" t="n">
-        <v>1295</v>
+        <v>1498</v>
       </c>
       <c r="P2" t="n">
-        <v>0.730400451212634</v>
+        <v>0.731088335773548</v>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="R2" t="n">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1415679639029893</v>
+        <v>0.1366520253782333</v>
       </c>
       <c r="T2" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U2" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="V2" t="n">
-        <v>0.104906937394247</v>
+        <v>0.1010248901903368</v>
       </c>
       <c r="W2" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="X2" t="n">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1206993795826283</v>
+        <v>0.1200585651537335</v>
       </c>
       <c r="Z2" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="AA2" t="n">
-        <v>549</v>
+        <v>647</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3096446700507614</v>
+        <v>0.3157637872132747</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7891891891891892</v>
+        <v>0.7817089452603472</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.398406374501992</v>
+        <v>0.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3763440860215054</v>
+        <v>0.3671497584541063</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3831775700934579</v>
+        <v>0.3861788617886179</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3351548269581057</v>
+        <v>0.3338485316846986</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.578378378378378</v>
+        <v>1.563417890520694</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.7342995169082126</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.045871559633027</v>
+        <v>1.044792833146696</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.888268156424581</v>
+        <v>0.9061728395061729</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.043046357615894</v>
+        <v>1.034782608695652</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.602836879432624</v>
+        <v>1.620915032679739</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.465714285714286</v>
+        <v>1.491183879093199</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.065714285714286</v>
+        <v>5.161209068010075</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.531428571428571</v>
+        <v>6.652392947103275</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.3814285714286</v>
+        <v>77.05500000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>76.24357142857143</v>
+        <v>76.89500000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>121.7432851481624</v>
+        <v>121.513102282333</v>
       </c>
       <c r="E3" t="n">
-        <v>108.8147946899504</v>
+        <v>110.7029065608947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5685279187817259</v>
+        <v>0.5683260126891166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1434026582755626</v>
+        <v>0.1412429378531073</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3261339092872571</v>
+        <v>0.3188539741219963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3288212069937959</v>
+        <v>0.3225963884821864</v>
       </c>
       <c r="J3" t="n">
-        <v>11.35714285714286</v>
+        <v>11.46875</v>
       </c>
       <c r="K3" t="n">
-        <v>11.25</v>
+        <v>11.15625</v>
       </c>
       <c r="L3" t="n">
-        <v>8.071428571428571</v>
+        <v>7.75</v>
       </c>
       <c r="M3" t="n">
-        <v>11.78571428571429</v>
+        <v>11.71875</v>
       </c>
       <c r="N3" t="n">
-        <v>36.5</v>
+        <v>36.59375</v>
       </c>
       <c r="O3" t="n">
-        <v>46.25</v>
+        <v>46.8125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.730400451212634</v>
+        <v>0.731088335773548</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.571428571428572</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>8.964285714285714</v>
+        <v>8.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1415679639029893</v>
+        <v>0.1366520253782333</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.375</v>
       </c>
       <c r="U3" t="n">
-        <v>6.642857142857143</v>
+        <v>6.46875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.104906937394247</v>
+        <v>0.1010248901903368</v>
       </c>
       <c r="W3" t="n">
-        <v>2.928571428571428</v>
+        <v>2.96875</v>
       </c>
       <c r="X3" t="n">
-        <v>7.642857142857143</v>
+        <v>7.6875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1206993795826283</v>
+        <v>0.1200585651537335</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.571428571428571</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.60714285714286</v>
+        <v>20.21875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3096446700507615</v>
+        <v>0.3157637872132747</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7891891891891892</v>
+        <v>0.7817089452603472</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3984063745019921</v>
+        <v>0.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3763440860215054</v>
+        <v>0.3671497584541063</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3831775700934579</v>
+        <v>0.3861788617886179</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3351548269581056</v>
+        <v>0.3338485316846986</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.578378378378378</v>
+        <v>1.563417890520694</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.7342995169082126</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.045871559633027</v>
+        <v>1.044792833146696</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.888268156424581</v>
+        <v>0.9061728395061729</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.043046357615894</v>
+        <v>1.034782608695652</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.602836879432624</v>
+        <v>1.620915032679739</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.465714285714286</v>
+        <v>1.491183879093199</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.065714285714286</v>
+        <v>5.161209068010075</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.531428571428571</v>
+        <v>6.652392947103275</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2130.96</v>
+        <v>2455.52</v>
       </c>
       <c r="C4" t="n">
-        <v>2134.82</v>
+        <v>2460.64</v>
       </c>
       <c r="D4" t="n">
-        <v>108.8147946899504</v>
+        <v>110.7029065608947</v>
       </c>
       <c r="E4" t="n">
-        <v>121.7432851481624</v>
+        <v>121.513102282333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5180229382850902</v>
+        <v>0.5290199809705043</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1470250024641062</v>
+        <v>0.1448228512579921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2965853658536585</v>
+        <v>0.2934595524956971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2326597487711633</v>
+        <v>0.2378686964795433</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="M4" t="n">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="N4" t="n">
-        <v>757</v>
+        <v>894</v>
       </c>
       <c r="O4" t="n">
-        <v>1041</v>
+        <v>1214</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5685417804478428</v>
+        <v>0.5775451950523312</v>
       </c>
       <c r="Q4" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="R4" t="n">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1654833424358274</v>
+        <v>0.164605137963844</v>
       </c>
       <c r="T4" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="U4" t="n">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1638448935008192</v>
+        <v>0.1598477640342531</v>
       </c>
       <c r="W4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="X4" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06772255598033862</v>
+        <v>0.07326355851569934</v>
       </c>
       <c r="Z4" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="AA4" t="n">
-        <v>622</v>
+        <v>710</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3397050791916985</v>
+        <v>0.3377735490009515</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7271853986551393</v>
+        <v>0.7364085667215815</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3993399339933993</v>
+        <v>0.4017341040462428</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.38</v>
+        <v>0.3839285714285715</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4112903225806452</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3279742765273312</v>
+        <v>0.3295774647887324</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.454370797310279</v>
+        <v>1.472817133443163</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.76</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.025469168900804</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8314285714285714</v>
+        <v>0.8337531486146096</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.032894736842105</v>
+        <v>1.020527859237537</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.636363636363636</v>
+        <v>1.647619047619048</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.273743016759777</v>
+        <v>1.325925925925926</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.114525139664805</v>
+        <v>5.190123456790124</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.388268156424581</v>
+        <v>6.51604938271605</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.10571428571428</v>
+        <v>76.735</v>
       </c>
       <c r="C5" t="n">
-        <v>76.24357142857143</v>
+        <v>76.89500000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>108.8147946899504</v>
+        <v>110.7029065608947</v>
       </c>
       <c r="E5" t="n">
-        <v>121.7432851481624</v>
+        <v>121.513102282333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5180229382850902</v>
+        <v>0.5290199809705043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1470250024641062</v>
+        <v>0.1448228512579921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2965853658536585</v>
+        <v>0.2934595524956971</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2326597487711633</v>
+        <v>0.2378686964795433</v>
       </c>
       <c r="J5" t="n">
-        <v>10.39285714285714</v>
+        <v>10.34375</v>
       </c>
       <c r="K5" t="n">
-        <v>11.21428571428571</v>
+        <v>10.875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.142857142857143</v>
+        <v>5.40625</v>
       </c>
       <c r="M5" t="n">
-        <v>11.75</v>
+        <v>11.6875</v>
       </c>
       <c r="N5" t="n">
-        <v>27.03571428571428</v>
+        <v>27.9375</v>
       </c>
       <c r="O5" t="n">
-        <v>37.17857142857143</v>
+        <v>37.9375</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5685417804478428</v>
+        <v>0.5775451950523312</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.321428571428571</v>
+        <v>4.34375</v>
       </c>
       <c r="R5" t="n">
-        <v>10.82142857142857</v>
+        <v>10.8125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1654833424358274</v>
+        <v>0.164605137963844</v>
       </c>
       <c r="T5" t="n">
-        <v>4.071428571428571</v>
+        <v>4.03125</v>
       </c>
       <c r="U5" t="n">
-        <v>10.71428571428571</v>
+        <v>10.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1638448935008192</v>
+        <v>0.1598477640342531</v>
       </c>
       <c r="W5" t="n">
-        <v>1.821428571428571</v>
+        <v>2.0625</v>
       </c>
       <c r="X5" t="n">
-        <v>4.428571428571429</v>
+        <v>4.8125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06772255598033862</v>
+        <v>0.07326355851569934</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.285714285714286</v>
+        <v>7.3125</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.21428571428572</v>
+        <v>22.1875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3397050791916986</v>
+        <v>0.3377735490009515</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7271853986551392</v>
+        <v>0.7364085667215815</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3993399339933993</v>
+        <v>0.4017341040462428</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.38</v>
+        <v>0.3839285714285715</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4112903225806451</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3279742765273312</v>
+        <v>0.3295774647887324</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.454370797310278</v>
+        <v>1.472817133443163</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.76</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.025469168900804</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8314285714285714</v>
+        <v>0.8337531486146096</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.032894736842105</v>
+        <v>1.020527859237537</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.636363636363636</v>
+        <v>1.647619047619048</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.273743016759776</v>
+        <v>1.325925925925926</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.114525139664804</v>
+        <v>5.190123456790124</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.38826815642458</v>
+        <v>6.51604938271605</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
+        <v>80</v>
+      </c>
+      <c r="H8" t="n">
+        <v>72</v>
+      </c>
+      <c r="I8" t="n">
+        <v>91</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46</v>
+      </c>
+      <c r="K8" t="n">
+        <v>94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>22</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R8" t="n">
+        <v>44</v>
+      </c>
+      <c r="S8" t="n">
         <v>67</v>
       </c>
-      <c r="H8" t="n">
-        <v>53</v>
-      </c>
-      <c r="I8" t="n">
-        <v>69</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" t="n">
-        <v>80</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>21</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>26</v>
-      </c>
-      <c r="R8" t="n">
-        <v>36</v>
-      </c>
-      <c r="S8" t="n">
-        <v>53</v>
-      </c>
       <c r="T8" t="n">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="U8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V8" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="W8" t="n">
         <v>7</v>
@@ -1488,87 +1488,87 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="Z8" t="n">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.759</v>
+        <v>0.773</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AH8" t="n">
         <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.423</v>
+        <v>0.406</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>421:07</t>
+          <t>493:56</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>215.36</v>
+        <v>264.04</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.607</v>
+        <v>0.618</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.068</v>
+        <v>1.087</v>
       </c>
       <c r="AS8" t="n">
         <v>0.121</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.577</v>
+        <v>1.438</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.235</v>
+        <v>0.244</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.046</v>
+        <v>0.053</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.208</v>
+        <v>0.21</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -1626,16 +1626,16 @@
         <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T9" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="U9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="V9" t="n">
         <v>17</v>
@@ -1647,87 +1647,87 @@
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.672</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB9" t="n">
         <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="AH9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.471</v>
+        <v>0.5</v>
       </c>
       <c r="AK9" t="n">
         <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.372</v>
+        <v>0.364</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>294:26</t>
+          <t>320:53</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>129.76</v>
+        <v>138.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.6</v>
+        <v>0.606</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.62</v>
+        <v>0.624</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.125</v>
+        <v>1.14</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.092</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.19</v>
+        <v>0.186</v>
       </c>
       <c r="AU9" t="n">
         <v>0.833</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.202</v>
+        <v>0.198</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.049</v>
+        <v>0.044</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
@@ -1737,40 +1737,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
         <v>5</v>
@@ -1779,114 +1779,114 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="U10" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
         <v>12</v>
       </c>
-      <c r="V10" t="n">
-        <v>9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
       <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="AB10" t="n">
         <v>5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3</v>
-      </c>
       <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AE10" t="n">
         <v>10</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>8</v>
-      </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.526</v>
       </c>
       <c r="AH10" t="n">
         <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.474</v>
+        <v>0.45</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.222</v>
+        <v>0.279</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>384:42</t>
+          <t>450:29</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>120.56</v>
+        <v>138.88</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.51</v>
+        <v>0.553</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.544</v>
+        <v>0.585</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.97</v>
+        <v>1.051</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.108</v>
+        <v>0.101</v>
       </c>
       <c r="AT10" t="n">
         <v>0.186</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>2.214</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.144</v>
+        <v>0.141</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="11">
@@ -1896,40 +1896,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>118</v>
+      </c>
+      <c r="H11" t="n">
+        <v>58</v>
+      </c>
+      <c r="I11" t="n">
+        <v>64</v>
+      </c>
+      <c r="J11" t="n">
+        <v>125</v>
+      </c>
+      <c r="K11" t="n">
         <v>43</v>
-      </c>
-      <c r="E11" t="n">
-        <v>76</v>
-      </c>
-      <c r="F11" t="n">
-        <v>35</v>
-      </c>
-      <c r="G11" t="n">
-        <v>106</v>
-      </c>
-      <c r="H11" t="n">
-        <v>54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>58</v>
-      </c>
-      <c r="J11" t="n">
-        <v>112</v>
-      </c>
-      <c r="K11" t="n">
-        <v>38</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
         <v>6</v>
@@ -1938,22 +1938,22 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="R11" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V11" t="n">
         <v>19</v>
@@ -1965,13 +1965,13 @@
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Z11" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.882</v>
+        <v>0.87</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
@@ -1992,60 +1992,60 @@
         <v>0.375</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.188</v>
+        <v>0.222</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AL11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.356</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>538:35</t>
+          <t>598:59</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>254.52</v>
+        <v>275.16</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.525</v>
+        <v>0.51</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.59</v>
+        <v>0.576</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.963</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="AT11" t="n">
         <v>0.297</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.383</v>
+        <v>2.404</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.217</v>
+        <v>0.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.141</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="12">
@@ -2055,82 +2055,82 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>23</v>
+      </c>
+      <c r="C12" t="n">
+        <v>152</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>82</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
         <v>20</v>
       </c>
-      <c r="C12" t="n">
-        <v>134</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" t="n">
-        <v>37</v>
-      </c>
-      <c r="F12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" t="n">
-        <v>74</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16</v>
+      </c>
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>56</v>
-      </c>
-      <c r="L12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M12" t="n">
-        <v>13</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>6</v>
-      </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V12" t="n">
         <v>25</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.757</v>
+        <v>0.762</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
@@ -2142,69 +2142,69 @@
         <v>0.167</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.457</v>
+        <v>0.463</v>
       </c>
       <c r="AK12" t="n">
         <v>12</v>
       </c>
       <c r="AL12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.308</v>
+        <v>0.293</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>384:51</t>
+          <t>449:26</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>122.28</v>
+        <v>136.16</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.576</v>
+        <v>0.588</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.096</v>
+        <v>1.116</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.167</v>
+        <v>2.857</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.146</v>
+        <v>0.139</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.159</v>
+        <v>0.148</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D13" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="n">
         <v>31</v>
       </c>
-      <c r="E13" t="n">
-        <v>37</v>
-      </c>
-      <c r="F13" t="n">
-        <v>27</v>
-      </c>
       <c r="G13" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L13" t="n">
+        <v>18</v>
+      </c>
+      <c r="M13" t="n">
         <v>14</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -2256,40 +2256,40 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>16</v>
+      </c>
+      <c r="R13" t="n">
+        <v>47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>175</v>
+      </c>
+      <c r="U13" t="n">
+        <v>27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>22</v>
+      </c>
+      <c r="X13" t="n">
         <v>14</v>
       </c>
-      <c r="Q13" t="n">
-        <v>14</v>
-      </c>
-      <c r="R13" t="n">
-        <v>35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>161</v>
-      </c>
-      <c r="U13" t="n">
-        <v>26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>20</v>
-      </c>
-      <c r="W13" t="n">
-        <v>20</v>
-      </c>
-      <c r="X13" t="n">
-        <v>13</v>
-      </c>
       <c r="Y13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="Z13" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.842</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB13" t="n">
         <v>3</v>
@@ -2310,57 +2310,57 @@
         <v>0.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>339:11</t>
+          <t>405:04</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>125.2</v>
+        <v>145.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.746</v>
+        <v>0.719</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.326</v>
+        <v>1.281</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.235</v>
+        <v>0.226</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.214</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.169</v>
+        <v>0.165</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.068</v>
+        <v>0.076</v>
       </c>
       <c r="AY13" t="n">
         <v>0.021</v>
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I14" t="n">
+        <v>116</v>
+      </c>
+      <c r="J14" t="n">
+        <v>49</v>
+      </c>
+      <c r="K14" t="n">
         <v>104</v>
       </c>
-      <c r="J14" t="n">
-        <v>39</v>
-      </c>
-      <c r="K14" t="n">
-        <v>86</v>
-      </c>
       <c r="L14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
         <v>24</v>
@@ -2415,114 +2415,114 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="R14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S14" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="T14" t="n">
-        <v>402</v>
+        <v>486</v>
       </c>
       <c r="U14" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="V14" t="n">
         <v>24</v>
       </c>
       <c r="W14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="Z14" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.387</v>
+        <v>0.364</v>
       </c>
       <c r="AE14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.348</v>
+        <v>0.333</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.407</v>
+        <v>0.438</v>
       </c>
       <c r="AK14" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.351</v>
+        <v>0.375</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>532:18</t>
+          <t>603:36</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>342.76</v>
+        <v>397.04</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.544</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.616</v>
+        <v>0.634</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.071</v>
+        <v>1.098</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.131</v>
+        <v>0.133</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.369</v>
+        <v>0.355</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.867</v>
+        <v>0.925</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.295</v>
+        <v>0.301</v>
       </c>
       <c r="AW14" t="n">
         <v>0.039</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.177</v>
+        <v>0.191</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="15">
@@ -2532,64 +2532,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="D15" t="n">
+        <v>51</v>
+      </c>
+      <c r="E15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
         <v>42</v>
       </c>
-      <c r="E15" t="n">
-        <v>83</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I15" t="n">
+        <v>122</v>
+      </c>
+      <c r="J15" t="n">
+        <v>90</v>
+      </c>
+      <c r="K15" t="n">
+        <v>46</v>
+      </c>
+      <c r="L15" t="n">
         <v>11</v>
       </c>
-      <c r="G15" t="n">
-        <v>31</v>
-      </c>
-      <c r="H15" t="n">
-        <v>94</v>
-      </c>
-      <c r="I15" t="n">
-        <v>108</v>
-      </c>
-      <c r="J15" t="n">
-        <v>72</v>
-      </c>
-      <c r="K15" t="n">
-        <v>43</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9</v>
-      </c>
       <c r="M15" t="n">
+        <v>13</v>
+      </c>
+      <c r="N15" t="n">
         <v>12</v>
       </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q15" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="R15" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="S15" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="T15" t="n">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V15" t="n">
         <v>13</v>
@@ -2601,22 +2601,22 @@
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="Z15" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.776</v>
+        <v>0.763</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.471</v>
+        <v>0.455</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -2628,48 +2628,48 @@
         <v>0.231</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.37</v>
+        <v>0.353</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>436:25</t>
+          <t>517:00</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>211.52</v>
+        <v>250.68</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.513</v>
+        <v>0.521</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.653</v>
+        <v>0.645</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.998</v>
+        <v>1.001</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.236</v>
+        <v>0.223</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.825</v>
+        <v>0.738</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.44</v>
+        <v>1.607</v>
       </c>
       <c r="AV15" t="n">
         <v>0.222</v>
@@ -2678,10 +2678,10 @@
         <v>0.025</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.108</v>
+        <v>0.098</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2709,25 +2709,25 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="n">
         <v>14</v>
       </c>
-      <c r="L16" t="n">
-        <v>9</v>
-      </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2739,43 +2739,43 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T16" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="W16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.868</v>
+        <v>0.827</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.6</v>
+        <v>0.417</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2806,38 +2806,38 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>103:27</t>
+          <t>164:52</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>42.6</v>
+        <v>60.24</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.781</v>
+        <v>0.681</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.803</v>
+        <v>0.72</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.455</v>
+        <v>1.345</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.094</v>
+        <v>0.066</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.375</v>
+        <v>0.362</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.189</v>
+        <v>0.167</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.148</v>
+        <v>0.134</v>
       </c>
       <c r="AY16" t="n">
         <v>0.005</v>
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
@@ -2874,16 +2874,16 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
@@ -2892,22 +2892,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T17" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="U17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V17" t="n">
         <v>14</v>
@@ -2919,13 +2919,13 @@
         <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Z17" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.765</v>
+        <v>0.789</v>
       </c>
       <c r="AB17" t="n">
         <v>7</v>
@@ -2940,66 +2940,66 @@
         <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AH17" t="n">
         <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.091</v>
+        <v>0.067</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>294:08</t>
+          <t>335:08</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>95.31999999999999</v>
+        <v>111.32</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.548</v>
+        <v>0.541</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.592</v>
+        <v>0.581</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.06</v>
+        <v>1.015</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.105</v>
+        <v>0.126</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.288</v>
+        <v>0.247</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.058</v>
+        <v>0.053</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.097</v>
+        <v>0.112</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="18">
@@ -3009,82 +3009,82 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L18" t="n">
+        <v>34</v>
+      </c>
+      <c r="M18" t="n">
+        <v>21</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>24</v>
+      </c>
+      <c r="R18" t="n">
+        <v>58</v>
+      </c>
+      <c r="S18" t="n">
+        <v>34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>199</v>
+      </c>
+      <c r="U18" t="n">
         <v>29</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20</v>
-      </c>
-      <c r="N18" t="n">
-        <v>26</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>22</v>
-      </c>
-      <c r="R18" t="n">
-        <v>51</v>
-      </c>
-      <c r="S18" t="n">
-        <v>27</v>
-      </c>
-      <c r="T18" t="n">
-        <v>178</v>
-      </c>
-      <c r="U18" t="n">
-        <v>24</v>
       </c>
       <c r="V18" t="n">
         <v>25</v>
       </c>
       <c r="W18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="Z18" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.762</v>
+        <v>0.738</v>
       </c>
       <c r="AB18" t="n">
         <v>6</v>
@@ -3117,45 +3117,45 @@
         <v>1</v>
       </c>
       <c r="AL18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>291:32</t>
+          <t>335:37</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>113.32</v>
+        <v>128.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.639</v>
+        <v>0.638</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.673</v>
+        <v>0.669</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.085</v>
+        <v>1.089</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.194</v>
+        <v>0.187</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.278</v>
+        <v>0.333</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.773</v>
+        <v>0.833</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.178</v>
+        <v>0.175</v>
       </c>
       <c r="AW18" t="n">
         <v>0.12</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="AY18" t="n">
         <v>0.021</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -3467,13 +3467,13 @@
         <v>0.25</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.239</v>
+        <v>0.234</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.18</v>
+        <v>0.182</v>
       </c>
       <c r="AY20" t="n">
         <v>0.001</v>
@@ -3626,16 +3626,16 @@
         <v>0.435</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.198</v>
+        <v>0.201</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="22">
@@ -3645,156 +3645,156 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J22" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S22" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="T22" t="n">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="V22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="W22" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="Z22" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.77</v>
+        <v>0.736</v>
       </c>
       <c r="AB22" t="n">
         <v>6</v>
       </c>
       <c r="AC22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.438</v>
+        <v>0.368</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="AL22" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.3</v>
+        <v>0.321</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>463:21</t>
+          <t>538:45</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>210.8</v>
+        <v>250.64</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.478</v>
+        <v>0.482</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.887</v>
+        <v>0.902</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.733</v>
+        <v>5.062</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.209</v>
+        <v>0.213</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3804,156 +3804,156 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C23" t="n">
+        <v>197</v>
+      </c>
+      <c r="D23" t="n">
+        <v>55</v>
+      </c>
+      <c r="E23" t="n">
+        <v>91</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>56</v>
+      </c>
+      <c r="H23" t="n">
+        <v>36</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48</v>
+      </c>
+      <c r="J23" t="n">
+        <v>55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22</v>
+      </c>
+      <c r="M23" t="n">
+        <v>15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>50</v>
+      </c>
+      <c r="S23" t="n">
+        <v>53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>243</v>
+      </c>
+      <c r="U23" t="n">
+        <v>17</v>
+      </c>
+      <c r="V23" t="n">
+        <v>33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>26</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>105</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC23" t="n">
         <v>23</v>
       </c>
-      <c r="C23" t="n">
-        <v>170</v>
-      </c>
-      <c r="D23" t="n">
-        <v>46</v>
-      </c>
-      <c r="E23" t="n">
-        <v>74</v>
-      </c>
-      <c r="F23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G23" t="n">
-        <v>45</v>
-      </c>
-      <c r="H23" t="n">
-        <v>33</v>
-      </c>
-      <c r="I23" t="n">
-        <v>42</v>
-      </c>
-      <c r="J23" t="n">
-        <v>47</v>
-      </c>
-      <c r="K23" t="n">
-        <v>47</v>
-      </c>
-      <c r="L23" t="n">
-        <v>18</v>
-      </c>
-      <c r="M23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>19</v>
-      </c>
-      <c r="R23" t="n">
-        <v>42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>46</v>
-      </c>
-      <c r="T23" t="n">
-        <v>213</v>
-      </c>
-      <c r="U23" t="n">
-        <v>9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>27</v>
-      </c>
-      <c r="W23" t="n">
-        <v>24</v>
-      </c>
-      <c r="X23" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>68</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>86</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>20</v>
-      </c>
       <c r="AD23" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AH23" t="n">
         <v>1</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.359</v>
+        <v>0.327</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>389:20</t>
+          <t>451:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>156.48</v>
+        <v>193.12</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.576</v>
+        <v>0.548</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.618</v>
+        <v>0.586</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.086</v>
+        <v>1.02</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.121</v>
+        <v>0.129</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.277</v>
+        <v>0.245</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.474</v>
+        <v>2.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.184</v>
+        <v>0.196</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3981,49 +3981,49 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I24" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L24" t="n">
+        <v>32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="n">
         <v>28</v>
       </c>
-      <c r="M24" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" t="n">
-        <v>26</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S24" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T24" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V24" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="W24" t="n">
         <v>9</v>
@@ -4032,31 +4032,31 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.704</v>
+        <v>0.697</v>
       </c>
       <c r="AB24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
@@ -4078,41 +4078,41 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>246:49</t>
+          <t>281:32</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>115.2</v>
+        <v>133.28</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.676</v>
+        <v>0.675</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.137</v>
+        <v>1.125</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.493</v>
+        <v>0.458</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.7</v>
+        <v>0.652</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.214</v>
+        <v>0.216</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.137</v>
+        <v>0.135</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.159</v>
+        <v>0.173</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -4262,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L26" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2990</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>893</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>741</v>
       </c>
       <c r="T27" t="n">
-        <v>66</v>
+        <v>3635</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1498</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>20</v>
+        <v>2810.76</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.619</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.064</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,157 +4595,157 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2599</v>
+        <v>2724</v>
       </c>
       <c r="D28" t="n">
-        <v>609</v>
+        <v>662</v>
       </c>
       <c r="E28" t="n">
-        <v>1010</v>
+        <v>1238</v>
       </c>
       <c r="F28" t="n">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="G28" t="n">
-        <v>763</v>
+        <v>864</v>
       </c>
       <c r="H28" t="n">
-        <v>583</v>
+        <v>500</v>
       </c>
       <c r="I28" t="n">
-        <v>722</v>
+        <v>658</v>
       </c>
       <c r="J28" t="n">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="K28" t="n">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="L28" t="n">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="M28" t="n">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="N28" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="Q28" t="n">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="R28" t="n">
-        <v>580</v>
+        <v>751</v>
       </c>
       <c r="S28" t="n">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="T28" t="n">
-        <v>3180</v>
+        <v>2946</v>
       </c>
       <c r="U28" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="V28" t="n">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="W28" t="n">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="X28" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="Y28" t="n">
-        <v>1022</v>
+        <v>894</v>
       </c>
       <c r="Z28" t="n">
-        <v>1295</v>
+        <v>1214</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.789</v>
+        <v>0.736</v>
       </c>
       <c r="AB28" t="n">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AC28" t="n">
-        <v>251</v>
+        <v>346</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.398</v>
+        <v>0.402</v>
       </c>
       <c r="AE28" t="n">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="AF28" t="n">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.376</v>
+        <v>0.384</v>
       </c>
       <c r="AH28" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="AI28" t="n">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.383</v>
+        <v>0.429</v>
       </c>
       <c r="AK28" t="n">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="AL28" t="n">
-        <v>549</v>
+        <v>710</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2440.68</v>
+        <v>2796.52</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.569</v>
+        <v>0.529</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.622</v>
+        <v>0.57</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.065</v>
+        <v>0.974</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.329</v>
+        <v>0.238</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.466</v>
+        <v>1.326</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.141</v>
+        <v>0.136</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,1910 +4754,1910 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2323</v>
-      </c>
-      <c r="D29" t="n">
-        <v>566</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1085</v>
-      </c>
-      <c r="F29" t="n">
-        <v>255</v>
-      </c>
-      <c r="G29" t="n">
-        <v>746</v>
-      </c>
-      <c r="H29" t="n">
-        <v>426</v>
-      </c>
-      <c r="I29" t="n">
-        <v>559</v>
-      </c>
-      <c r="J29" t="n">
-        <v>456</v>
-      </c>
-      <c r="K29" t="n">
-        <v>624</v>
-      </c>
-      <c r="L29" t="n">
-        <v>304</v>
-      </c>
-      <c r="M29" t="n">
-        <v>190</v>
-      </c>
-      <c r="N29" t="n">
-        <v>171</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>358</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>329</v>
-      </c>
-      <c r="R29" t="n">
-        <v>653</v>
-      </c>
-      <c r="S29" t="n">
-        <v>574</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2488</v>
-      </c>
-      <c r="U29" t="n">
-        <v>291</v>
-      </c>
-      <c r="V29" t="n">
-        <v>314</v>
-      </c>
-      <c r="W29" t="n">
-        <v>144</v>
-      </c>
-      <c r="X29" t="n">
-        <v>88</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>757</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1041</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>121</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>303</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>114</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>300</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>51</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>124</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>204</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>622</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5600:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2434.96</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.274</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#0 T. LYLES (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11.958</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.792</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="T30" t="n">
+        <v>356</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>11.002</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.06900000000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#0 T. LYLES (Per Game)</t>
+          <t>#1 D. KRAMER (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>10.952</v>
+        <v>5.852</v>
       </c>
       <c r="D31" t="n">
-        <v>2.286</v>
+        <v>1.148</v>
       </c>
       <c r="E31" t="n">
-        <v>4.381</v>
+        <v>1.889</v>
       </c>
       <c r="F31" t="n">
-        <v>1.286</v>
+        <v>0.926</v>
       </c>
       <c r="G31" t="n">
-        <v>3.19</v>
+        <v>2.296</v>
       </c>
       <c r="H31" t="n">
-        <v>2.524</v>
+        <v>0.778</v>
       </c>
       <c r="I31" t="n">
-        <v>3.286</v>
+        <v>1.148</v>
       </c>
       <c r="J31" t="n">
-        <v>1.952</v>
+        <v>0.37</v>
       </c>
       <c r="K31" t="n">
-        <v>3.81</v>
+        <v>1.185</v>
       </c>
       <c r="L31" t="n">
-        <v>0.762</v>
+        <v>0.444</v>
       </c>
       <c r="M31" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.889</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T31" t="n">
+        <v>138</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0.333</v>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.238</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.238</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.524</v>
-      </c>
-      <c r="T31" t="n">
-        <v>286</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3.905</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.143</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.524</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.238</v>
-      </c>
       <c r="AI31" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.048</v>
+        <v>0.593</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.476</v>
+        <v>1.63</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.423</v>
+        <v>0.364</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>10.255</v>
+        <v>5.135</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.607</v>
+        <v>0.624</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.068</v>
+        <v>1.14</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.121</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.333</v>
+        <v>0.186</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.577</v>
+        <v>0.833</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.235</v>
+        <v>0.198</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.208</v>
+        <v>0.11</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#1 D. KRAMER (Per Game)</t>
+          <t>#6 A. ABALDE (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C32" t="n">
-        <v>6.083</v>
+        <v>5.407</v>
       </c>
       <c r="D32" t="n">
-        <v>1.125</v>
+        <v>1.148</v>
       </c>
       <c r="E32" t="n">
-        <v>1.875</v>
+        <v>1.852</v>
       </c>
       <c r="F32" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.208</v>
-      </c>
       <c r="J32" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="T32" t="n">
+        <v>136</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.417</v>
       </c>
-      <c r="K32" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="T32" t="n">
-        <v>130</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.417</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AE32" t="n">
-        <v>0.167</v>
+        <v>0.37</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.25</v>
+        <v>0.704</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.667</v>
+        <v>0.526</v>
       </c>
       <c r="AH32" t="n">
         <v>0.333</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.708</v>
+        <v>0.741</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.471</v>
+        <v>0.45</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.792</v>
+        <v>1.593</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.372</v>
+        <v>0.279</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.407</v>
+        <v>5.144</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.6</v>
+        <v>0.553</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.62</v>
+        <v>0.585</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.125</v>
+        <v>1.051</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.092</v>
+        <v>0.101</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.19</v>
+        <v>0.186</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.833</v>
+        <v>2.214</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.202</v>
+        <v>0.141</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.049</v>
+        <v>0.018</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.108</v>
+        <v>0.074</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#6 A. ABALDE (Per Game)</t>
+          <t>#7 F. CAMPAZZO (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C33" t="n">
-        <v>5.087</v>
+        <v>9.519</v>
       </c>
       <c r="D33" t="n">
-        <v>1.043</v>
+        <v>1.63</v>
       </c>
       <c r="E33" t="n">
-        <v>1.826</v>
+        <v>2.852</v>
       </c>
       <c r="F33" t="n">
-        <v>0.739</v>
+        <v>1.37</v>
       </c>
       <c r="G33" t="n">
-        <v>2.391</v>
+        <v>4.37</v>
       </c>
       <c r="H33" t="n">
-        <v>0.783</v>
+        <v>2.148</v>
       </c>
       <c r="I33" t="n">
-        <v>1.043</v>
+        <v>2.37</v>
       </c>
       <c r="J33" t="n">
-        <v>1.13</v>
+        <v>4.63</v>
       </c>
       <c r="K33" t="n">
-        <v>1.217</v>
+        <v>1.593</v>
       </c>
       <c r="L33" t="n">
-        <v>0.217</v>
+        <v>0.148</v>
       </c>
       <c r="M33" t="n">
-        <v>0.391</v>
+        <v>1.111</v>
       </c>
       <c r="N33" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.926</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.926</v>
       </c>
       <c r="R33" t="n">
-        <v>1.565</v>
+        <v>2.148</v>
       </c>
       <c r="S33" t="n">
-        <v>0.913</v>
+        <v>3.185</v>
       </c>
       <c r="T33" t="n">
-        <v>100</v>
+        <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>0.522</v>
+        <v>0.963</v>
       </c>
       <c r="V33" t="n">
-        <v>0.391</v>
+        <v>0.704</v>
       </c>
       <c r="W33" t="n">
-        <v>0.391</v>
+        <v>0.778</v>
       </c>
       <c r="X33" t="n">
-        <v>0.217</v>
+        <v>0.481</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.348</v>
+        <v>3.222</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.739</v>
+        <v>3.704</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.775</v>
+        <v>0.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.13</v>
+        <v>0.444</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.435</v>
+        <v>1.222</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.3</v>
+        <v>0.364</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.348</v>
+        <v>0.111</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.696</v>
+        <v>0.296</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.391</v>
+        <v>0.148</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.826</v>
+        <v>0.667</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.474</v>
+        <v>0.222</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.348</v>
+        <v>1.222</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.565</v>
+        <v>3.704</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.222</v>
+        <v>0.33</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>5.242</v>
+        <v>10.191</v>
       </c>
       <c r="AP33" t="n">
         <v>0.51</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.544</v>
+        <v>0.576</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.97</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.108</v>
+        <v>0.189</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.186</v>
+        <v>0.297</v>
       </c>
       <c r="AU33" t="n">
-        <v>2</v>
+        <v>2.404</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.144</v>
+        <v>0.21</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.038</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#7 F. CAMPAZZO (Per Game)</t>
+          <t>#8 C. OKEKE (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
-        <v>10.208</v>
+        <v>6.609</v>
       </c>
       <c r="D34" t="n">
-        <v>1.792</v>
+        <v>1.043</v>
       </c>
       <c r="E34" t="n">
-        <v>3.167</v>
+        <v>1.783</v>
       </c>
       <c r="F34" t="n">
-        <v>1.458</v>
+        <v>1.348</v>
       </c>
       <c r="G34" t="n">
-        <v>4.417</v>
+        <v>3.565</v>
       </c>
       <c r="H34" t="n">
-        <v>2.25</v>
+        <v>0.478</v>
       </c>
       <c r="I34" t="n">
-        <v>2.417</v>
+        <v>0.609</v>
       </c>
       <c r="J34" t="n">
-        <v>4.667</v>
+        <v>0.87</v>
       </c>
       <c r="K34" t="n">
-        <v>1.583</v>
+        <v>2.609</v>
       </c>
       <c r="L34" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="T34" t="n">
+        <v>195</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.167</v>
       </c>
-      <c r="M34" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="T34" t="n">
-        <v>300</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.958</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3.417</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.364</v>
-      </c>
       <c r="AE34" t="n">
-        <v>0.125</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.333</v>
+        <v>0.304</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.375</v>
+        <v>0.286</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.125</v>
+        <v>0.826</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.667</v>
+        <v>1.783</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.188</v>
+        <v>0.463</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.333</v>
+        <v>0.522</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.75</v>
+        <v>1.783</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.356</v>
+        <v>0.293</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>10.605</v>
+        <v>5.92</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.525</v>
+        <v>0.573</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.59</v>
+        <v>0.588</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.963</v>
+        <v>1.116</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.185</v>
+        <v>0.051</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.297</v>
+        <v>0.089</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.383</v>
+        <v>2.857</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.217</v>
+        <v>0.139</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.077</v>
+        <v>0.148</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.167</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#8 C. OKEKE (Per Game)</t>
+          <t>#9 G. PROCIDA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C35" t="n">
-        <v>6.7</v>
+        <v>6.448</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.172</v>
       </c>
       <c r="E35" t="n">
-        <v>1.85</v>
+        <v>1.448</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4</v>
+        <v>1.069</v>
       </c>
       <c r="G35" t="n">
-        <v>3.7</v>
+        <v>2.517</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5</v>
+        <v>0.897</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.172</v>
       </c>
       <c r="J35" t="n">
-        <v>0.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>2.8</v>
+        <v>0.966</v>
       </c>
       <c r="L35" t="n">
-        <v>1.2</v>
+        <v>0.621</v>
       </c>
       <c r="M35" t="n">
-        <v>0.65</v>
+        <v>0.483</v>
       </c>
       <c r="N35" t="n">
-        <v>0.35</v>
+        <v>0.138</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3</v>
+        <v>0.552</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3</v>
+        <v>0.552</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.621</v>
       </c>
       <c r="S35" t="n">
-        <v>0.85</v>
+        <v>0.862</v>
       </c>
       <c r="T35" t="n">
         <v>175</v>
       </c>
       <c r="U35" t="n">
-        <v>0.65</v>
+        <v>0.931</v>
       </c>
       <c r="V35" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AU35" t="n">
         <v>1.25</v>
       </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>19:14</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>6.114</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.167</v>
-      </c>
       <c r="AV35" t="n">
-        <v>0.146</v>
+        <v>0.165</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.075</v>
+        <v>0.053</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.159</v>
+        <v>0.076</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PROCIDA (Per Game)</t>
+          <t>#11 M. HEZONJA (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" t="n">
-        <v>6.64</v>
+        <v>16.769</v>
       </c>
       <c r="D36" t="n">
-        <v>1.24</v>
+        <v>3.154</v>
       </c>
       <c r="E36" t="n">
-        <v>1.48</v>
+        <v>5.731</v>
       </c>
       <c r="F36" t="n">
-        <v>1.08</v>
+        <v>2.154</v>
       </c>
       <c r="G36" t="n">
-        <v>2.44</v>
+        <v>5.538</v>
       </c>
       <c r="H36" t="n">
-        <v>0.92</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>4.462</v>
       </c>
       <c r="J36" t="n">
-        <v>0.68</v>
+        <v>1.885</v>
       </c>
       <c r="K36" t="n">
-        <v>0.84</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="M36" t="n">
-        <v>0.52</v>
+        <v>0.923</v>
       </c>
       <c r="N36" t="n">
-        <v>0.16</v>
+        <v>0.154</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.038</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.038</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>0.962</v>
       </c>
       <c r="S36" t="n">
-        <v>0.88</v>
+        <v>3.615</v>
       </c>
       <c r="T36" t="n">
-        <v>161</v>
+        <v>486</v>
       </c>
       <c r="U36" t="n">
-        <v>1.04</v>
+        <v>2.385</v>
       </c>
       <c r="V36" t="n">
-        <v>0.8</v>
+        <v>0.923</v>
       </c>
       <c r="W36" t="n">
-        <v>0.8</v>
+        <v>1.462</v>
       </c>
       <c r="X36" t="n">
-        <v>0.52</v>
+        <v>0.885</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.92</v>
+        <v>6.038</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.28</v>
+        <v>6.962</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.842</v>
+        <v>0.867</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.12</v>
+        <v>0.462</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.24</v>
+        <v>1.269</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.5</v>
+        <v>0.364</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.12</v>
+        <v>0.654</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.16</v>
+        <v>1.962</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.76</v>
+        <v>0.538</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.48</v>
+        <v>1.231</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.514</v>
+        <v>0.437</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.32</v>
+        <v>1.615</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.96</v>
+        <v>4.308</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>23:12</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.008</v>
+        <v>15.271</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.73</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.746</v>
+        <v>0.634</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.326</v>
+        <v>1.098</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.112</v>
+        <v>0.133</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.235</v>
+        <v>0.355</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.214</v>
+        <v>0.925</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.169</v>
+        <v>0.301</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.068</v>
+        <v>0.191</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.024</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#11 M. HEZONJA (Per Game)</t>
+          <t>#12 T. MALEDON (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C37" t="n">
-        <v>15.957</v>
+        <v>9.654</v>
       </c>
       <c r="D37" t="n">
-        <v>3.087</v>
+        <v>1.962</v>
       </c>
       <c r="E37" t="n">
-        <v>5.696</v>
+        <v>3.808</v>
       </c>
       <c r="F37" t="n">
-        <v>1.913</v>
+        <v>0.577</v>
       </c>
       <c r="G37" t="n">
-        <v>5.261</v>
+        <v>1.615</v>
       </c>
       <c r="H37" t="n">
-        <v>4.043</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>4.522</v>
+        <v>4.692</v>
       </c>
       <c r="J37" t="n">
-        <v>1.696</v>
+        <v>3.462</v>
       </c>
       <c r="K37" t="n">
-        <v>3.739</v>
+        <v>1.769</v>
       </c>
       <c r="L37" t="n">
-        <v>0.739</v>
+        <v>0.423</v>
       </c>
       <c r="M37" t="n">
-        <v>1.043</v>
+        <v>0.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0.174</v>
+        <v>0.462</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.957</v>
+        <v>2.154</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.957</v>
+        <v>2.154</v>
       </c>
       <c r="R37" t="n">
-        <v>1.043</v>
+        <v>2.308</v>
       </c>
       <c r="S37" t="n">
-        <v>3.565</v>
+        <v>3.923</v>
       </c>
       <c r="T37" t="n">
-        <v>402</v>
+        <v>316</v>
       </c>
       <c r="U37" t="n">
-        <v>2.522</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="V37" t="n">
-        <v>1.043</v>
+        <v>0.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.478</v>
+        <v>0.654</v>
       </c>
       <c r="X37" t="n">
-        <v>0.913</v>
+        <v>0.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.913</v>
+        <v>5.462</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.87</v>
+        <v>7.154</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.861</v>
+        <v>0.763</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.522</v>
+        <v>0.385</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.348</v>
+        <v>0.846</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.387</v>
+        <v>0.455</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.696</v>
+        <v>0.115</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.348</v>
+        <v>0.231</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.478</v>
+        <v>0.115</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.174</v>
+        <v>0.308</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.407</v>
+        <v>0.375</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.435</v>
+        <v>0.462</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.087</v>
+        <v>1.308</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>14.903</v>
+        <v>9.641999999999999</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.544</v>
+        <v>0.521</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.616</v>
+        <v>0.645</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.071</v>
+        <v>1.001</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.131</v>
+        <v>0.223</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.369</v>
+        <v>0.738</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.867</v>
+        <v>1.607</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.295</v>
+        <v>0.222</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.177</v>
+        <v>0.098</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.065</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#12 T. MALEDON (Per Game)</t>
+          <t>#13 I. ALMANSA (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C38" t="n">
-        <v>9.590999999999999</v>
+        <v>3.857</v>
       </c>
       <c r="D38" t="n">
-        <v>1.909</v>
+        <v>1.524</v>
       </c>
       <c r="E38" t="n">
-        <v>3.773</v>
+        <v>2.19</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.409</v>
+        <v>0.048</v>
       </c>
       <c r="H38" t="n">
-        <v>4.273</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>4.909</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.273</v>
+        <v>0.238</v>
       </c>
       <c r="K38" t="n">
-        <v>1.955</v>
+        <v>0.952</v>
       </c>
       <c r="L38" t="n">
-        <v>0.409</v>
+        <v>0.667</v>
       </c>
       <c r="M38" t="n">
-        <v>0.545</v>
+        <v>0.143</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.273</v>
+        <v>0.19</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.273</v>
+        <v>0.19</v>
       </c>
       <c r="R38" t="n">
-        <v>2.455</v>
+        <v>1.333</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>0.762</v>
       </c>
       <c r="T38" t="n">
-        <v>267</v>
+        <v>95</v>
       </c>
       <c r="U38" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.381</v>
       </c>
       <c r="V38" t="n">
-        <v>0.591</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W38" t="n">
-        <v>0.773</v>
+        <v>0.333</v>
       </c>
       <c r="X38" t="n">
-        <v>0.591</v>
+        <v>0.238</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.682</v>
+        <v>2.048</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.318</v>
+        <v>2.476</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.776</v>
+        <v>0.827</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.364</v>
+        <v>0.238</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.773</v>
+        <v>0.571</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.471</v>
+        <v>0.417</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.136</v>
+        <v>0.048</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.591</v>
+        <v>0.143</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.231</v>
+        <v>0.333</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.227</v>
+        <v>0.048</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>9.615</v>
+        <v>2.869</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.513</v>
+        <v>0.681</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.653</v>
+        <v>0.72</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.998</v>
+        <v>1.345</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.236</v>
+        <v>0.066</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.825</v>
+        <v>0.362</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.025</v>
+        <v>0.101</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.108</v>
+        <v>0.134</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.113</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#13 I. ALMANSA (Per Game)</t>
+          <t>#14 G. DECK (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>3.647</v>
+        <v>7.062</v>
       </c>
       <c r="D39" t="n">
-        <v>1.471</v>
+        <v>2.125</v>
       </c>
       <c r="E39" t="n">
-        <v>1.824</v>
+        <v>3.375</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G39" t="n">
-        <v>0.059</v>
+        <v>1.938</v>
       </c>
       <c r="H39" t="n">
-        <v>0.706</v>
+        <v>1.312</v>
       </c>
       <c r="I39" t="n">
-        <v>0.882</v>
+        <v>1.75</v>
       </c>
       <c r="J39" t="n">
-        <v>0.235</v>
+        <v>0.875</v>
       </c>
       <c r="K39" t="n">
-        <v>0.824</v>
+        <v>2.125</v>
       </c>
       <c r="L39" t="n">
-        <v>0.529</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>0.118</v>
+        <v>0.625</v>
       </c>
       <c r="N39" t="n">
-        <v>0.294</v>
+        <v>0.125</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.235</v>
+        <v>0.875</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.235</v>
+        <v>0.875</v>
       </c>
       <c r="R39" t="n">
-        <v>1.176</v>
+        <v>1.688</v>
       </c>
       <c r="S39" t="n">
-        <v>0.647</v>
+        <v>1.75</v>
       </c>
       <c r="T39" t="n">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="U39" t="n">
-        <v>0.353</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V39" t="n">
-        <v>0.647</v>
+        <v>0.875</v>
       </c>
       <c r="W39" t="n">
-        <v>0.353</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="X39" t="n">
-        <v>0.235</v>
+        <v>0.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.941</v>
+        <v>2.812</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.235</v>
+        <v>3.562</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.868</v>
+        <v>0.789</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.176</v>
+        <v>0.438</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.294</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.6</v>
+        <v>0.467</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.059</v>
+        <v>0.188</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.176</v>
+        <v>0.625</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.059</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2.506</v>
+        <v>6.958</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.781</v>
+        <v>0.541</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.803</v>
+        <v>0.581</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.455</v>
+        <v>1.015</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.094</v>
+        <v>0.126</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.375</v>
+        <v>0.247</v>
       </c>
       <c r="AU39" t="n">
         <v>1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.189</v>
+        <v>0.152</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.105</v>
+        <v>0.053</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.148</v>
+        <v>0.112</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.008</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#14 G. DECK (Per Game)</t>
+          <t>#16 U. GARUBA (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C40" t="n">
-        <v>7.214</v>
+        <v>5.185</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>3.357</v>
+        <v>3.148</v>
       </c>
       <c r="F40" t="n">
-        <v>0.571</v>
+        <v>0.037</v>
       </c>
       <c r="G40" t="n">
-        <v>1.857</v>
+        <v>0.074</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>1.074</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.481</v>
       </c>
       <c r="J40" t="n">
-        <v>0.929</v>
+        <v>0.741</v>
       </c>
       <c r="K40" t="n">
-        <v>1.857</v>
+        <v>1.778</v>
       </c>
       <c r="L40" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="M40" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="T40" t="n">
+        <v>199</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.815</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.143</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="T40" t="n">
-        <v>111</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.786</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.643</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AM40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC40" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AG40" t="n">
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>4.763</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="AT40" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>6.809</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.288</v>
-      </c>
       <c r="AU40" t="n">
-        <v>1.3</v>
+        <v>0.833</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.149</v>
+        <v>0.175</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.058</v>
+        <v>0.12</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.097</v>
+        <v>0.158</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#16 U. GARUBA (Per Game)</t>
+          <t>#17 E. AMOSOV (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
         <v>0</v>
@@ -6669,145 +6669,145 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>00:36</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>4.533</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.639</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.673</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.085</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#17 E. AMOSOV (Per Game)</t>
+          <t>#20 B. FERNANDO (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="T42" t="n">
+        <v>15</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -6838,60 +6838,60 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>01:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>5.253</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#20 B. FERNANDO (Per Game)</t>
+          <t>#22 W. TAVARES (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>8.909000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>1.667</v>
+        <v>3.273</v>
       </c>
       <c r="E43" t="n">
-        <v>3.333</v>
+        <v>4.273</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -6900,82 +6900,82 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.667</v>
+        <v>2.364</v>
       </c>
       <c r="I43" t="n">
-        <v>1.333</v>
+        <v>3.136</v>
       </c>
       <c r="J43" t="n">
-        <v>0.333</v>
+        <v>0.455</v>
       </c>
       <c r="K43" t="n">
-        <v>1.667</v>
+        <v>3.773</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>2.318</v>
       </c>
       <c r="M43" t="n">
-        <v>0.667</v>
+        <v>0.727</v>
       </c>
       <c r="N43" t="n">
-        <v>0.333</v>
+        <v>2.182</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.333</v>
+        <v>1.045</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.333</v>
+        <v>1.045</v>
       </c>
       <c r="R43" t="n">
-        <v>1.667</v>
+        <v>2.727</v>
       </c>
       <c r="S43" t="n">
-        <v>1.333</v>
+        <v>3.136</v>
       </c>
       <c r="T43" t="n">
-        <v>15</v>
+        <v>351</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="V43" t="n">
-        <v>0.333</v>
+        <v>1.955</v>
       </c>
       <c r="W43" t="n">
-        <v>0.667</v>
+        <v>0.227</v>
       </c>
       <c r="X43" t="n">
-        <v>0.333</v>
+        <v>0.182</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>4.864</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.667</v>
+        <v>5.864</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.545</v>
+        <v>0.829</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.333</v>
+        <v>0.636</v>
       </c>
       <c r="AC43" t="n">
-        <v>1</v>
+        <v>1.273</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -6997,621 +6997,621 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>5.253</v>
+        <v>6.698</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.5</v>
+        <v>0.766</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.51</v>
+        <v>0.788</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.761</v>
+        <v>1.33</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.254</v>
+        <v>0.156</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.2</v>
+        <v>0.553</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.25</v>
+        <v>0.435</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.238</v>
+        <v>0.147</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.239</v>
+        <v>0.133</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.18</v>
+        <v>0.201</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#22 W. TAVARES (Per Game)</t>
+          <t>#23 S. LLULL (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>8.909000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="D44" t="n">
-        <v>3.273</v>
+        <v>1.032</v>
       </c>
       <c r="E44" t="n">
-        <v>4.273</v>
+        <v>2.355</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.419</v>
       </c>
       <c r="H44" t="n">
-        <v>2.364</v>
+        <v>1.548</v>
       </c>
       <c r="I44" t="n">
-        <v>3.136</v>
+        <v>1.806</v>
       </c>
       <c r="J44" t="n">
-        <v>0.455</v>
+        <v>2.613</v>
       </c>
       <c r="K44" t="n">
-        <v>3.773</v>
+        <v>1.194</v>
       </c>
       <c r="L44" t="n">
-        <v>2.318</v>
+        <v>0.226</v>
       </c>
       <c r="M44" t="n">
-        <v>0.727</v>
+        <v>0.452</v>
       </c>
       <c r="N44" t="n">
-        <v>2.182</v>
+        <v>0.032</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.045</v>
+        <v>0.516</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.045</v>
+        <v>0.516</v>
       </c>
       <c r="R44" t="n">
-        <v>2.727</v>
+        <v>1.323</v>
       </c>
       <c r="S44" t="n">
-        <v>3.136</v>
+        <v>1.323</v>
       </c>
       <c r="T44" t="n">
-        <v>351</v>
+        <v>202</v>
       </c>
       <c r="U44" t="n">
-        <v>0.545</v>
+        <v>0.968</v>
       </c>
       <c r="V44" t="n">
-        <v>1.955</v>
+        <v>0.806</v>
       </c>
       <c r="W44" t="n">
-        <v>0.227</v>
+        <v>1.129</v>
       </c>
       <c r="X44" t="n">
-        <v>0.182</v>
+        <v>0.581</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.864</v>
+        <v>2.161</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.864</v>
+        <v>2.935</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.829</v>
+        <v>0.736</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.636</v>
+        <v>0.194</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.273</v>
+        <v>0.613</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.5</v>
+        <v>0.316</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.136</v>
+        <v>0.226</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.273</v>
+        <v>0.613</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.5</v>
+        <v>0.368</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.129</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>3.516</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>6.698</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.766</v>
+        <v>0.424</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.788</v>
+        <v>0.482</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.33</v>
+        <v>0.902</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.156</v>
+        <v>0.064</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.553</v>
+        <v>0.229</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.435</v>
+        <v>5.062</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.148</v>
+        <v>0.213</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.135</v>
+        <v>0.015</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.198</v>
+        <v>0.076</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.016</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#23 S. LLULL (Per Game)</t>
+          <t>#24 A. FELIZ (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>27</v>
       </c>
       <c r="C45" t="n">
-        <v>6.926</v>
+        <v>7.296</v>
       </c>
       <c r="D45" t="n">
-        <v>1.111</v>
+        <v>2.037</v>
       </c>
       <c r="E45" t="n">
-        <v>2.333</v>
+        <v>3.37</v>
       </c>
       <c r="F45" t="n">
-        <v>1.074</v>
+        <v>0.63</v>
       </c>
       <c r="G45" t="n">
-        <v>4.185</v>
+        <v>2.074</v>
       </c>
       <c r="H45" t="n">
-        <v>1.481</v>
+        <v>1.333</v>
       </c>
       <c r="I45" t="n">
-        <v>1.667</v>
+        <v>1.778</v>
       </c>
       <c r="J45" t="n">
-        <v>2.63</v>
+        <v>2.037</v>
       </c>
       <c r="K45" t="n">
-        <v>1.296</v>
+        <v>2.037</v>
       </c>
       <c r="L45" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="T45" t="n">
+        <v>243</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.889</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AI45" t="n">
         <v>0.259</v>
       </c>
-      <c r="M45" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="T45" t="n">
-        <v>171</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.148</v>
-      </c>
-      <c r="X45" t="n">
+      <c r="AJ45" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.593</v>
       </c>
-      <c r="Y45" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.741</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1</v>
-      </c>
       <c r="AL45" t="n">
-        <v>3.333</v>
+        <v>1.815</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.3</v>
+        <v>0.327</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.807</v>
+        <v>7.153</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.418</v>
+        <v>0.548</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.478</v>
+        <v>0.586</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.887</v>
+        <v>1.02</v>
       </c>
       <c r="AS45" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AY45" t="n">
         <v>0.07099999999999999</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#24 A. FELIZ (Per Game)</t>
+          <t>#25 A. LEN (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>23</v>
       </c>
       <c r="C46" t="n">
-        <v>7.391</v>
+        <v>6.522</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>2.435</v>
       </c>
       <c r="E46" t="n">
-        <v>3.217</v>
+        <v>3.565</v>
       </c>
       <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.652</v>
       </c>
-      <c r="G46" t="n">
-        <v>1.957</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.435</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.043</v>
-      </c>
       <c r="K46" t="n">
-        <v>2.043</v>
+        <v>1.913</v>
       </c>
       <c r="L46" t="n">
-        <v>0.783</v>
+        <v>1.391</v>
       </c>
       <c r="M46" t="n">
-        <v>0.435</v>
+        <v>0.478</v>
       </c>
       <c r="N46" t="n">
-        <v>0.13</v>
+        <v>1.217</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.826</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.826</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.826</v>
+        <v>1.652</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>1.739</v>
       </c>
       <c r="T46" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="U46" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="W46" t="n">
         <v>0.391</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.174</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.043</v>
-      </c>
       <c r="X46" t="n">
-        <v>0.696</v>
+        <v>0.217</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.957</v>
+        <v>3.696</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.739</v>
+        <v>5.304</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.791</v>
+        <v>0.697</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.304</v>
+        <v>0.348</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.87</v>
+        <v>0.739</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.35</v>
+        <v>0.471</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.174</v>
+        <v>0.043</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.435</v>
+        <v>0.217</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
         <v>0.043</v>
       </c>
-      <c r="AI46" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1.696</v>
-      </c>
       <c r="AM46" t="n">
-        <v>0.359</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>6.803</v>
+        <v>5.795</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.576</v>
+        <v>0.675</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.618</v>
+        <v>0.68</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.086</v>
+        <v>1.125</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.121</v>
+        <v>0.173</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.277</v>
+        <v>0.458</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.474</v>
+        <v>0.652</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.184</v>
+        <v>0.216</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.056</v>
+        <v>0.135</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.132</v>
+        <v>0.173</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#25 A. LEN (Per Game)</t>
+          <t>#33 G. GRINVALDS (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>6.238</v>
+        <v>0.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2.286</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.048</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.667</v>
+        <v>0.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.619</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.238</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.619</v>
+        <v>0.5</v>
       </c>
       <c r="T47" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.095</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0.238</v>
+        <v>0.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.619</v>
+        <v>0.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.143</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.704</v>
+        <v>0.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -7626,61 +7626,61 @@
         <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.048</v>
+        <v>0.5</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>00:33</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.486</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.676</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.137</v>
+        <v>0.532</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.493</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.214</v>
+        <v>0.781</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.159</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#33 G. GRINVALDS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -7692,22 +7692,22 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1.812</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.344</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,16 +7719,16 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -7740,19 +7740,19 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -7785,39 +7785,39 @@
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.784</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
         <v>0</v>
@@ -7832,157 +7832,157 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>93.438</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>21.812</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>36.125</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>9.718999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>27.906</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>20.656</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>25.906</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="K49" t="n">
-        <v>1.786</v>
+        <v>25.656</v>
       </c>
       <c r="L49" t="n">
-        <v>1.393</v>
+        <v>10.781</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>7.031</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.031</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.714</v>
+        <v>12.406</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>11.719</v>
       </c>
       <c r="R49" t="n">
-        <v>0.107</v>
+        <v>20.844</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>23.156</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3635</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>11.469</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>11.156</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.781</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>36.594</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>46.812</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>6.469</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.969</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>7.688</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>20.219</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>87.836</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.619</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.064</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>85.125</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>20.688</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>38.688</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9.375</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>15.625</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>20.562</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>16.781</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>23.031</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>10.656</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6.688</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>12.656</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>11.688</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>23.469</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>20.594</v>
       </c>
       <c r="T50" t="n">
-        <v>66</v>
+        <v>2946</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>10.344</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>10.875</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>5.406</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.281</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>27.938</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>37.938</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.736</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>4.344</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>10.812</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>4.031</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.062</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.812</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>7.312</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>22.188</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>0.714</v>
+        <v>87.39100000000001</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.974</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.326</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>92.821</v>
-      </c>
-      <c r="D51" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="E51" t="n">
-        <v>36.071</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="H51" t="n">
-        <v>20.821</v>
-      </c>
-      <c r="I51" t="n">
-        <v>25.786</v>
-      </c>
-      <c r="J51" t="n">
-        <v>18.321</v>
-      </c>
-      <c r="K51" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="L51" t="n">
-        <v>10.786</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6.964</v>
-      </c>
-      <c r="N51" t="n">
-        <v>6.214</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>11.786</v>
-      </c>
-      <c r="R51" t="n">
-        <v>20.714</v>
-      </c>
-      <c r="S51" t="n">
-        <v>22.964</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3180</v>
-      </c>
-      <c r="U51" t="n">
-        <v>11.357</v>
-      </c>
-      <c r="V51" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="W51" t="n">
-        <v>8.071</v>
-      </c>
-      <c r="X51" t="n">
-        <v>5.036</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>46.25</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>3.571</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>8.964</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>6.643</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.929</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7.643</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>6.571</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>19.607</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>87.167</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.466</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>82.964</v>
-      </c>
-      <c r="D52" t="n">
-        <v>20.214</v>
-      </c>
-      <c r="E52" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.106999999999999</v>
-      </c>
-      <c r="G52" t="n">
-        <v>26.643</v>
-      </c>
-      <c r="H52" t="n">
-        <v>15.214</v>
-      </c>
-      <c r="I52" t="n">
-        <v>19.964</v>
-      </c>
-      <c r="J52" t="n">
-        <v>16.286</v>
-      </c>
-      <c r="K52" t="n">
-        <v>22.286</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10.857</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6.786</v>
-      </c>
-      <c r="N52" t="n">
-        <v>6.107</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>12.786</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="R52" t="n">
-        <v>23.321</v>
-      </c>
-      <c r="S52" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2488</v>
-      </c>
-      <c r="U52" t="n">
-        <v>10.393</v>
-      </c>
-      <c r="V52" t="n">
-        <v>11.214</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5.143</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.143</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>27.036</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>37.179</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>4.321</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>10.821</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>4.071</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>10.714</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>4.429</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>7.286</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>22.214</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>86.96299999999999</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.274</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>
